--- a/src/app/data/RAG 系统评估指标结果.xlsx
+++ b/src/app/data/RAG 系统评估指标结果.xlsx
@@ -1,28 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/laixiangran/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/laixiangran/lai-workspace/ai-learn/src/app/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A088EE2-0669-2F48-85A9-469CF7AA70A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E691E599-0B59-E24C-9C58-3323D1C9DDCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2000" yWindow="1500" windowWidth="28240" windowHeight="17440" activeTab="1" xr2:uid="{752BAC88-3D22-6345-9E5D-6A586CA68B77}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="1" xr2:uid="{752BAC88-3D22-6345-9E5D-6A586CA68B77}"/>
   </bookViews>
   <sheets>
-    <sheet name="04_问题优化" sheetId="3" r:id="rId1"/>
-    <sheet name="结果汇总" sheetId="1" r:id="rId2"/>
-    <sheet name="指标说明" sheetId="2" r:id="rId3"/>
+    <sheet name="06_检索优化 (1)" sheetId="5" r:id="rId1"/>
+    <sheet name="05_切分优化" sheetId="4" r:id="rId2"/>
+    <sheet name="04_问题优化" sheetId="3" r:id="rId3"/>
+    <sheet name="结果汇总" sheetId="1" r:id="rId4"/>
+    <sheet name="指标说明" sheetId="2" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="100">
   <si>
     <t>版本</t>
   </si>
@@ -471,12 +473,240 @@
     <t>5. 答案正确性：衡量实际答案的准确性，需与参考答案对比。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>v7.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v7.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>知识库：markdown 文档
+切分方法：RecursiveCharacterTextSplitter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>知识库：markdown 文档
+切分方法：MarkdownTextSplitter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>答案忠实度（faithfulness）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>问题：原问题
+知识库：单一文档（pdf 文档）
+切分方法：RecursiveCharacterTextSplitter
+文本切分大小（chunkSize）：500
+文本切分重叠大小（chunkOverlap）：50
+向量模型：nomic-embed-text
+检索 topK：3
+生成模型：qwen2.5:14b
+评估模型：qwen2.5:14b
+评估数据：/data/qa_test_10_new.json</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>描述2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检索 topK：3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检索 topK：1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检索 topK：2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检索 topK：4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检索 topK：5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检索 topK：6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检索 topK：7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检索 topK：8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>检索 topK：9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v7.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>知识库：markdown 文档
+切分方法：RecursiveCharacterTextSplitter（separators: ['\n## ', '\n### ']）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>问题：原问题
+知识库：单一文档（pdf 文档）
+切分方法：RecursiveCharacterTextSplitter
+文本切分大小（chunkSize）：500
+文本切分重叠大小（chunkOverlap）：50
+向量模型：nomic-embed-text
+检索 topK：3
+生成模型：qwen2.5:14b
+评估模型：qwen2.5:14b
+评估数据：/data/qa_test_10.json</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>版本配置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v4.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v4.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>版本说明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>知识库：多文档混合
+其它同 v1.0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>问题：对原问题意图识别
+其它同 v2.0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>问题：对原问题同义改写
+其它同 v3.0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>问题：对原问题多视角分解
+其它同 v3.0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>问题：对原问题补充上下文
+其它同 v3.0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基础版本
+作为后续一系列优化方法的效果对比</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>验证知识库混入多文档对 RAG 系统的影响</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对原问题进行意图识别，
+减少多文档带来的影响</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对原问题进行同义改写，
+优化检索效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对原问题进行多视角分解，
+优化检索效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对原问题进行上下文补充，
+优化检索效果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v5.0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v5.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>问题：原问题
+知识库：markdown 文档
+切分方法：RecursiveCharacterTextSplitter
+文本切分大小（chunkSize）：500
+文本切分重叠大小（chunkOverlap）：50
+向量模型：nomic-embed-text
+检索 topK：3
+生成模型：qwen2.5:14b
+评估模型：qwen2.5:14b
+评估数据：/data/qa_test_10.json</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v5.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v5.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>切分方法：MarkdownTextSplitter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">切分方法：在 MarkdownTextSplitter 基础上合并 chunkSize 小于 100 的文档块 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>切分方法：在 MarkdownTextSplitter 基础上合并 chunkSize 小于 100 的文档块以及给每个文档添加所在每一级别标题</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>切分方法：在 MarkdownTextSplitter 基础上给每个文档添加n个模拟问题</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v5.4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v5.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>切分方法：将每个文档块的模拟问题单独向量化，将基于模拟问题检索到的文档块 和 v5.3 检索到的文档块进行合并</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>切分方法：将每个文档块的模拟问题单独向量化，并基于模拟问题检索相应文档块</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="29">
+  <fonts count="20">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -606,6 +836,7 @@
     </font>
     <font>
       <sz val="10"/>
+      <color theme="1"/>
       <name val="等线"/>
       <family val="4"/>
       <charset val="134"/>
@@ -616,69 +847,7 @@
       <name val="等线"/>
       <family val="4"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -694,7 +863,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -730,13 +899,52 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -794,40 +1002,70 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -840,7 +1078,12 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="47">
+    <dxf>
+      <font>
+        <color rgb="FF00B14D"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFE0300"/>
@@ -849,6 +1092,76 @@
     <dxf>
       <font>
         <color rgb="FF00B14D"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFE0300"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B14D"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFE0300"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFE0300"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B14D"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B14D"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFE0300"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
       </font>
     </dxf>
     <dxf>
@@ -903,7 +1216,52 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFFE0300"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
       </font>
     </dxf>
     <dxf>
@@ -928,6 +1286,11 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFFE0300"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF00B14D"/>
       </font>
     </dxf>
@@ -941,8 +1304,23 @@
         <color rgb="FF00B14D"/>
       </font>
     </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B14D"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFE0300"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFF89671"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1250,6 +1628,1624 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83BFA76A-A23C-6842-8E58-EAE845D4A447}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="B2:I30"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="16.5" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="3.1640625" customWidth="1"/>
+    <col min="2" max="2" width="5.33203125" customWidth="1"/>
+    <col min="3" max="3" width="31.1640625" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" customWidth="1"/>
+    <col min="5" max="9" width="26.83203125" customWidth="1"/>
+    <col min="10" max="10" width="26.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" ht="16.5" customHeight="1">
+      <c r="B2" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" ht="140" customHeight="1">
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="20"/>
+      <c r="E3" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="F3" s="8">
+        <v>0.43</v>
+      </c>
+      <c r="G3" s="8">
+        <v>0.72</v>
+      </c>
+      <c r="H3" s="8">
+        <v>0.48</v>
+      </c>
+      <c r="I3" s="8">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" ht="33" customHeight="1">
+      <c r="B4" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" s="8">
+        <v>0.23</v>
+      </c>
+      <c r="F4" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="G4" s="8">
+        <v>0.66</v>
+      </c>
+      <c r="H4" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="I4" s="8">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" ht="33" customHeight="1">
+      <c r="B5" s="32"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="E5" s="8">
+        <v>0.34</v>
+      </c>
+      <c r="F5" s="8">
+        <v>0.65</v>
+      </c>
+      <c r="G5" s="8">
+        <v>0.78</v>
+      </c>
+      <c r="H5" s="8">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="I5" s="8">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" ht="33" customHeight="1">
+      <c r="B6" s="32"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="E6" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="F6" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="G6" s="8">
+        <v>0.84</v>
+      </c>
+      <c r="H6" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="I6" s="8">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" ht="33" customHeight="1">
+      <c r="B7" s="32"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="E7" s="8">
+        <v>0.42</v>
+      </c>
+      <c r="F7" s="8">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="G7" s="8">
+        <v>0.76</v>
+      </c>
+      <c r="H7" s="8">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="I7" s="8">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" ht="33" customHeight="1">
+      <c r="B8" s="32"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="E8" s="8">
+        <v>0.43</v>
+      </c>
+      <c r="F8" s="8">
+        <v>0.52</v>
+      </c>
+      <c r="G8" s="8">
+        <v>0.84</v>
+      </c>
+      <c r="H8" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="I8" s="8">
+        <v>0.57999999999999996</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" ht="33" customHeight="1">
+      <c r="B9" s="32"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0.52</v>
+      </c>
+      <c r="F9" s="8">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G9" s="8">
+        <v>0.91</v>
+      </c>
+      <c r="H9" s="8">
+        <v>0.43</v>
+      </c>
+      <c r="I9" s="8">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" ht="33" customHeight="1">
+      <c r="B10" s="32"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" s="8">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="F10" s="8">
+        <v>0.49</v>
+      </c>
+      <c r="G10" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="H10" s="8">
+        <v>0.53</v>
+      </c>
+      <c r="I10" s="8">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" ht="33" customHeight="1">
+      <c r="B11" s="32"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0.52</v>
+      </c>
+      <c r="F11" s="8">
+        <v>0.44</v>
+      </c>
+      <c r="G11" s="8">
+        <v>0.87</v>
+      </c>
+      <c r="H11" s="8">
+        <v>0.43</v>
+      </c>
+      <c r="I11" s="8">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" ht="46" customHeight="1">
+      <c r="B12" s="33"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0.54</v>
+      </c>
+      <c r="F12" s="8">
+        <v>0.46</v>
+      </c>
+      <c r="G12" s="8">
+        <v>0.85</v>
+      </c>
+      <c r="H12" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="I12" s="8">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" ht="46" customHeight="1">
+      <c r="B13" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+    </row>
+    <row r="14" spans="2:9" ht="46" customHeight="1">
+      <c r="B14" s="32"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+    </row>
+    <row r="15" spans="2:9" ht="46" customHeight="1">
+      <c r="B15" s="32"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+    </row>
+    <row r="16" spans="2:9" ht="46" customHeight="1">
+      <c r="B16" s="32"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+    </row>
+    <row r="17" spans="2:9" ht="46" customHeight="1">
+      <c r="B17" s="32"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+    </row>
+    <row r="18" spans="2:9" ht="46" customHeight="1">
+      <c r="B18" s="32"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0.52</v>
+      </c>
+      <c r="F18" s="8">
+        <v>0.45</v>
+      </c>
+      <c r="G18" s="8">
+        <v>0.82</v>
+      </c>
+      <c r="H18" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="I18" s="8">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" ht="46" customHeight="1">
+      <c r="B19" s="32"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+    </row>
+    <row r="20" spans="2:9" ht="46" customHeight="1">
+      <c r="B20" s="32"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+    </row>
+    <row r="21" spans="2:9" ht="33" customHeight="1">
+      <c r="B21" s="33"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+    </row>
+    <row r="22" spans="2:9" ht="46" customHeight="1">
+      <c r="B22" s="31" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+    </row>
+    <row r="23" spans="2:9" ht="46" customHeight="1">
+      <c r="B23" s="32"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+    </row>
+    <row r="24" spans="2:9" ht="46" customHeight="1">
+      <c r="B24" s="32"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+    </row>
+    <row r="25" spans="2:9" ht="46" customHeight="1">
+      <c r="B25" s="32"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+    </row>
+    <row r="26" spans="2:9" ht="46" customHeight="1">
+      <c r="B26" s="32"/>
+      <c r="C26" s="35"/>
+      <c r="D26" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+    </row>
+    <row r="27" spans="2:9" ht="46" customHeight="1">
+      <c r="B27" s="32"/>
+      <c r="C27" s="35"/>
+      <c r="D27" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="E27" s="8">
+        <v>0.49</v>
+      </c>
+      <c r="F27" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="G27" s="8">
+        <v>0.91</v>
+      </c>
+      <c r="H27" s="8">
+        <v>0.43</v>
+      </c>
+      <c r="I27" s="8">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" ht="46" customHeight="1">
+      <c r="B28" s="32"/>
+      <c r="C28" s="35"/>
+      <c r="D28" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+    </row>
+    <row r="29" spans="2:9" ht="46" customHeight="1">
+      <c r="B29" s="32"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+    </row>
+    <row r="30" spans="2:9" ht="33" customHeight="1">
+      <c r="B30" s="33"/>
+      <c r="C30" s="36"/>
+      <c r="D30" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="B4:B12"/>
+    <mergeCell ref="C4:C12"/>
+    <mergeCell ref="B13:B21"/>
+    <mergeCell ref="C13:C21"/>
+    <mergeCell ref="B22:B30"/>
+    <mergeCell ref="C22:C30"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="E3:E13 E15:E22 E24:E30">
+    <cfRule type="cellIs" dxfId="46" priority="35" operator="greaterThan">
+      <formula>0.5</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="45" priority="34" operator="lessThan">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5:I5">
+    <cfRule type="dataBar" priority="15">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFBAC6F8"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{799AA421-9FAE-9540-9F66-7829C866154A}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="25">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCDA7B"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{DD571C54-5F9F-924D-BAA5-39A08A609054}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="24">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFBAC6F8"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{BDC52813-7112-3B4E-ABCA-9D2846FB4236}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="23">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFF99570"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{19CC04DE-B1FE-5841-B6E6-3DDBD3D44E58}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="22">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF7DDFE7"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{6BE560D1-02B8-3741-957B-148E4955A767}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="21">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFDFB9EB"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{57EE048F-379B-774D-875C-2ED515DC452C}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="20">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF7BE5BB"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{0696D2A9-42CA-7246-AA3E-73F17C16E754}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="19">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCDA7B"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{F01E47F2-89F1-C444-AB7E-42F801B4962C}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="18">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFBAC6F8"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{B3467C43-1D33-AB48-8695-AD81DD88C417}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="17">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFF99570"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{F8CE1320-0FAA-DF45-AE75-6521D1216F35}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="16">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFF99570"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{F449C4A6-8AC2-5140-A907-64794CF7A6B7}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="14">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFF99570"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{25477AA2-18BD-EE45-A477-DC593098217D}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F30">
+    <cfRule type="cellIs" dxfId="44" priority="32" operator="lessThan">
+      <formula>0.43</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="43" priority="33" operator="greaterThan">
+      <formula>0.43</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5">
+    <cfRule type="dataBar" priority="13">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCDA7B"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{245237B8-ED1D-1044-AC4A-109EAEFA1808}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="12">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFBAC6F8"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{DDA361B5-2ABE-6B41-8AA7-861D28E0CA2C}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="11">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFF99570"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{D4C67D78-9145-5D40-9AD9-AE95FF79EF24}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="10">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF7DDFE7"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{8068B1DA-7D22-214C-8D0D-76243CCA2A5C}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="9">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFDFB9EB"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{1EAFA712-8BB4-F84F-8ABC-9FC881958D4A}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="8">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF7BE5BB"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{243A9755-04D9-AD48-A83E-D1E1DD2D8801}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="7">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCDA7B"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{E71D8BC7-AD9A-9C49-9D75-8CEB348BE1EA}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="6">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFBAC6F8"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{C515C054-BD10-8343-8F8A-65C7651AE4BF}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="5">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFF99570"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{75484FA4-C3AC-0B47-969B-E9915DB46D14}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="4">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFF99570"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{465D0531-80C6-1842-9069-B81E151316FA}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="3">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFBAC6F8"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{C4A3FB4A-FF8F-1345-B8F6-9183523E6A79}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F14:I14 E3:I13 E24:I30 F23:I23 E15:I22">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFF89671"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{2E8A0B47-D2B4-824B-91BE-674460DC79F8}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="2">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFF99570"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{1D8A6074-57F4-2343-A82D-1E53F8FEEE38}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F14:I14 E6:I13 E3:I4 E24:I30 F23:I23 E15:I22">
+    <cfRule type="dataBar" priority="36">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFF99570"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{9263CB1B-4AD3-F946-AF33-9FC9282420F9}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="37">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFBAC6F8"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{84FD3C84-0BEF-1C40-9144-124444AF7853}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="38">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFF99570"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{3C67E345-73E6-BF42-BD4C-E5E3E2FCFB23}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="39">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFF99570"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{93245084-69E5-F843-8820-72B14FC8C67A}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="40">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFBAC6F8"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{97B85A0F-77C1-4B4D-944F-67E8B97B32DD}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="41">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCDA7B"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{BFCC8FD6-0C05-694D-9A60-BE24BF5C7DBD}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="42">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF7BE5BB"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{B3FB3B9F-8424-4144-B42E-523655075382}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="43">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFDFB9EB"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{1801AAF1-004B-FD4C-9DFF-36D30E5E32F2}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="44">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF7DDFE7"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{B50B6A3A-3AFD-1341-B67C-7714517E8C3D}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="45">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFF99570"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{AFA4F68A-C33B-AF41-956D-A15C72FCA7F8}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="46">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFBAC6F8"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{4A8810A0-2C49-904A-81F0-5EB93BEDCEBD}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="47">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCDA7B"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{DEC5252D-4AEA-F14B-93A0-073E2D814FA9}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3:G30">
+    <cfRule type="cellIs" dxfId="42" priority="30" operator="lessThan">
+      <formula>0.72</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="41" priority="31" operator="greaterThan">
+      <formula>0.72</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3:H30">
+    <cfRule type="cellIs" dxfId="40" priority="29" operator="greaterThan">
+      <formula>0.48</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="39" priority="28" operator="lessThan">
+      <formula>0.48</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3:I30">
+    <cfRule type="cellIs" dxfId="38" priority="27" operator="greaterThan">
+      <formula>0.65</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="37" priority="26" operator="lessThan">
+      <formula>0.65</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{799AA421-9FAE-9540-9F66-7829C866154A}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{DD571C54-5F9F-924D-BAA5-39A08A609054}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{BDC52813-7112-3B4E-ABCA-9D2846FB4236}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{19CC04DE-B1FE-5841-B6E6-3DDBD3D44E58}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{6BE560D1-02B8-3741-957B-148E4955A767}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{57EE048F-379B-774D-875C-2ED515DC452C}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{0696D2A9-42CA-7246-AA3E-73F17C16E754}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{F01E47F2-89F1-C444-AB7E-42F801B4962C}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{B3467C43-1D33-AB48-8695-AD81DD88C417}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{F8CE1320-0FAA-DF45-AE75-6521D1216F35}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{F449C4A6-8AC2-5140-A907-64794CF7A6B7}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{25477AA2-18BD-EE45-A477-DC593098217D}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E5:I5</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{245237B8-ED1D-1044-AC4A-109EAEFA1808}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{DDA361B5-2ABE-6B41-8AA7-861D28E0CA2C}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{D4C67D78-9145-5D40-9AD9-AE95FF79EF24}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{8068B1DA-7D22-214C-8D0D-76243CCA2A5C}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{1EAFA712-8BB4-F84F-8ABC-9FC881958D4A}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{243A9755-04D9-AD48-A83E-D1E1DD2D8801}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{E71D8BC7-AD9A-9C49-9D75-8CEB348BE1EA}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{C515C054-BD10-8343-8F8A-65C7651AE4BF}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{75484FA4-C3AC-0B47-969B-E9915DB46D14}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{465D0531-80C6-1842-9069-B81E151316FA}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{C4A3FB4A-FF8F-1345-B8F6-9183523E6A79}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>F5</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{2E8A0B47-D2B4-824B-91BE-674460DC79F8}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{1D8A6074-57F4-2343-A82D-1E53F8FEEE38}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>F14:I14 E3:I13 E24:I30 F23:I23 E15:I22</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{9263CB1B-4AD3-F946-AF33-9FC9282420F9}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{84FD3C84-0BEF-1C40-9144-124444AF7853}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{3C67E345-73E6-BF42-BD4C-E5E3E2FCFB23}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{93245084-69E5-F843-8820-72B14FC8C67A}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{97B85A0F-77C1-4B4D-944F-67E8B97B32DD}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{BFCC8FD6-0C05-694D-9A60-BE24BF5C7DBD}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{B3FB3B9F-8424-4144-B42E-523655075382}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{1801AAF1-004B-FD4C-9DFF-36D30E5E32F2}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{B50B6A3A-3AFD-1341-B67C-7714517E8C3D}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{AFA4F68A-C33B-AF41-956D-A15C72FCA7F8}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{4A8810A0-2C49-904A-81F0-5EB93BEDCEBD}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{DEC5252D-4AEA-F14B-93A0-073E2D814FA9}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>F14:I14 E6:I13 E3:I4 E24:I30 F23:I23 E15:I22</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EA75820-A4D8-2D44-A926-21F65AF543E7}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="B2:H9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="16.5" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="3.1640625" customWidth="1"/>
+    <col min="2" max="2" width="6.83203125" customWidth="1"/>
+    <col min="3" max="3" width="31.1640625" customWidth="1"/>
+    <col min="4" max="4" width="26.83203125" customWidth="1"/>
+    <col min="5" max="7" width="26.83203125" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="26.83203125" customWidth="1"/>
+    <col min="9" max="9" width="26.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:8" ht="16.5" customHeight="1">
+      <c r="B2" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" ht="140" customHeight="1">
+      <c r="B3" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.41</v>
+      </c>
+      <c r="E3" s="8">
+        <v>0.53</v>
+      </c>
+      <c r="F3" s="8">
+        <v>0.84</v>
+      </c>
+      <c r="G3" s="8">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="H3" s="8">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" ht="46" customHeight="1">
+      <c r="B4" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="D4" s="27">
+        <v>0.44</v>
+      </c>
+      <c r="E4" s="27">
+        <v>0.6</v>
+      </c>
+      <c r="F4" s="27">
+        <v>0.84</v>
+      </c>
+      <c r="G4" s="27">
+        <v>0.64</v>
+      </c>
+      <c r="H4" s="27">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="46" customHeight="1">
+      <c r="B5" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="D5" s="27">
+        <v>0.54</v>
+      </c>
+      <c r="E5" s="27">
+        <v>0.6</v>
+      </c>
+      <c r="F5" s="27">
+        <v>0.93</v>
+      </c>
+      <c r="G5" s="27">
+        <v>0.66</v>
+      </c>
+      <c r="H5" s="27">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" ht="58" customHeight="1">
+      <c r="B6" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="D6" s="27">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="E6" s="27">
+        <v>0.83</v>
+      </c>
+      <c r="F6" s="27">
+        <v>0.89</v>
+      </c>
+      <c r="G6" s="27">
+        <v>0.66</v>
+      </c>
+      <c r="H6" s="27">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" ht="58" customHeight="1">
+      <c r="B7" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="D7" s="27">
+        <v>0.52</v>
+      </c>
+      <c r="E7" s="27">
+        <v>0.6</v>
+      </c>
+      <c r="F7" s="27">
+        <v>0.84</v>
+      </c>
+      <c r="G7" s="27">
+        <v>0.39</v>
+      </c>
+      <c r="H7" s="27">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" ht="58" customHeight="1">
+      <c r="B8" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="D8" s="27">
+        <v>0.52</v>
+      </c>
+      <c r="E8" s="27">
+        <v>0.43</v>
+      </c>
+      <c r="F8" s="27">
+        <v>0.84</v>
+      </c>
+      <c r="G8" s="27">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="H8" s="27">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" ht="58" customHeight="1">
+      <c r="B9" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="D9" s="27">
+        <v>0.65</v>
+      </c>
+      <c r="E9" s="27">
+        <v>0.51</v>
+      </c>
+      <c r="F9" s="27">
+        <v>0.82</v>
+      </c>
+      <c r="G9" s="27">
+        <v>0.23</v>
+      </c>
+      <c r="H9" s="27">
+        <v>0.59</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="D3:D9">
+    <cfRule type="cellIs" dxfId="36" priority="19" operator="lessThan">
+      <formula>0.41</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="35" priority="20" operator="greaterThan">
+      <formula>0.41</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D3:H13">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFF89671"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{765E8C6F-B24F-2344-804B-60FF8007DA57}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3:E9">
+    <cfRule type="cellIs" dxfId="34" priority="17" stopIfTrue="1" operator="lessThan">
+      <formula>0.53</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="33" priority="18" stopIfTrue="1" operator="greaterThan">
+      <formula>0.53</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F9">
+    <cfRule type="cellIs" dxfId="32" priority="15" stopIfTrue="1" operator="lessThan">
+      <formula>0.84</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="31" priority="16" stopIfTrue="1" operator="greaterThan">
+      <formula>0.84</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3:G9">
+    <cfRule type="cellIs" dxfId="30" priority="3" operator="lessThan">
+      <formula>0.55</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="29" priority="14" operator="greaterThan">
+      <formula>0.55</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3:H9">
+    <cfRule type="cellIs" dxfId="28" priority="4" operator="lessThan">
+      <formula>0.48</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="27" priority="5" operator="greaterThan">
+      <formula>0.48</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{765E8C6F-B24F-2344-804B-60FF8007DA57}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FF00B050"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D3:H13</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DB82AAA-112A-DB40-A193-37924261AA0C}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -1294,7 +3290,7 @@
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="9" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="8">
@@ -1340,7 +3336,7 @@
       <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="10" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="8">
@@ -1363,7 +3359,7 @@
       <c r="B6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="11" t="s">
         <v>14</v>
       </c>
       <c r="D6" s="8">
@@ -1386,7 +3382,7 @@
       <c r="B7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="12" t="s">
         <v>16</v>
       </c>
       <c r="D7" s="7">
@@ -1409,7 +3405,7 @@
       <c r="B8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D8" s="8">
@@ -1432,7 +3428,7 @@
       <c r="B9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="C9" s="14" t="s">
         <v>20</v>
       </c>
       <c r="D9" s="8">
@@ -1455,7 +3451,7 @@
       <c r="B10" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="15" t="s">
         <v>22</v>
       </c>
       <c r="D10" s="8">
@@ -1478,7 +3474,7 @@
       <c r="B11" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="26" t="s">
+      <c r="C11" s="16" t="s">
         <v>24</v>
       </c>
       <c r="D11" s="8">
@@ -1501,7 +3497,7 @@
       <c r="B12" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="27" t="s">
+      <c r="C12" s="17" t="s">
         <v>26</v>
       </c>
       <c r="D12" s="8">
@@ -1524,7 +3520,7 @@
       <c r="B13" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="28" t="s">
+      <c r="C13" s="18" t="s">
         <v>28</v>
       </c>
       <c r="D13" s="8">
@@ -1544,33 +3540,33 @@
       </c>
     </row>
     <row r="15" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B15" s="29" t="s">
+      <c r="B15" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
     </row>
     <row r="16" spans="2:8" ht="40.5" customHeight="1">
-      <c r="B16" s="30"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38"/>
     </row>
     <row r="17" spans="2:8" ht="159" customHeight="1">
-      <c r="B17" s="30"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="30"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="38"/>
     </row>
     <row r="20" spans="2:8" ht="16.5" customHeight="1">
       <c r="B20" s="5"/>
@@ -1587,10 +3583,10 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="D3:D13">
-    <cfRule type="cellIs" dxfId="9" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="26" priority="9" operator="lessThan">
       <formula>0.5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="10" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="25" priority="10" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1741,34 +3737,34 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:E13">
-    <cfRule type="cellIs" dxfId="7" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="24" priority="7" operator="lessThan">
       <formula>0.43</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="23" priority="8" operator="greaterThan">
       <formula>0.43</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F13">
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="22" priority="5" operator="lessThan">
       <formula>0.72</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="21" priority="6" operator="greaterThan">
       <formula>0.72</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G13">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="20" priority="3" operator="lessThan">
       <formula>0.48</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="19" priority="4" operator="greaterThan">
       <formula>0.48</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H13">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="18" priority="1" operator="lessThan">
       <formula>0.65</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="17" priority="2" operator="greaterThan">
       <formula>0.65</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1781,7 +3777,7 @@
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:negativeFillColor rgb="FFF89671"/>
               <x14:axisColor auto="1"/>
             </x14:dataBar>
           </x14:cfRule>
@@ -1881,354 +3877,518 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5088EADD-559C-4545-8302-492772DE53B5}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" customWidth="1"/>
-    <col min="2" max="2" width="31.1640625" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
-    <col min="4" max="4" width="28.6640625" customWidth="1"/>
-    <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="6" width="26.83203125" customWidth="1"/>
-    <col min="7" max="7" width="27.6640625" customWidth="1"/>
+    <col min="1" max="1" width="6.83203125" customWidth="1"/>
+    <col min="2" max="3" width="32.83203125" customWidth="1"/>
+    <col min="4" max="8" width="26.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="16.5" customHeight="1">
+    <row r="1" spans="1:8" ht="16.5" customHeight="1">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="C1" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="122.25" customHeight="1">
+    <row r="2" spans="1:8" ht="140" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="8">
+      <c r="B2" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2" s="8">
         <v>0.5</v>
       </c>
-      <c r="D2" s="8">
+      <c r="E2" s="8">
         <v>0.43</v>
       </c>
-      <c r="E2" s="8">
+      <c r="F2" s="8">
         <v>0.72</v>
       </c>
-      <c r="F2" s="8">
+      <c r="G2" s="8">
         <v>0.48</v>
       </c>
-      <c r="G2" s="8">
+      <c r="H2" s="8">
         <v>0.65</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.5" customHeight="1">
+    <row r="3" spans="1:8" ht="36" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="8">
+      <c r="B3" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3" s="8">
         <v>0.36</v>
       </c>
-      <c r="D3" s="8">
+      <c r="E3" s="8">
         <v>0.3</v>
       </c>
-      <c r="E3" s="8">
+      <c r="F3" s="8">
         <v>0.53</v>
       </c>
-      <c r="F3" s="8">
+      <c r="G3" s="8">
         <v>0.24</v>
       </c>
-      <c r="G3" s="8">
+      <c r="H3" s="8">
         <v>0.48</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="27.75" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="8">
+    <row r="4" spans="1:8" ht="36" customHeight="1">
+      <c r="A4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="E4" s="8">
         <v>0.43</v>
       </c>
-      <c r="D4" s="8">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="E4" s="8">
-        <v>0.61</v>
-      </c>
       <c r="F4" s="8">
+        <v>0.72</v>
+      </c>
+      <c r="G4" s="8">
+        <v>0.48</v>
+      </c>
+      <c r="H4" s="8">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="36" customHeight="1">
+      <c r="A5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.39</v>
+      </c>
+      <c r="E5" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="F5" s="8">
+        <v>0.72</v>
+      </c>
+      <c r="G5" s="8">
+        <v>0.54</v>
+      </c>
+      <c r="H5" s="8">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="36" customHeight="1">
+      <c r="A6" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" s="24">
+        <v>0.42</v>
+      </c>
+      <c r="E6" s="24">
+        <v>0.4</v>
+      </c>
+      <c r="F6" s="24">
+        <v>0.74</v>
+      </c>
+      <c r="G6" s="24">
         <v>0.43</v>
       </c>
-      <c r="G4" s="8">
-        <v>0.61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="27.75" customHeight="1">
-      <c r="A5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="D5" s="8">
-        <v>0.43</v>
-      </c>
-      <c r="E5" s="8">
-        <v>0.72</v>
-      </c>
-      <c r="F5" s="8">
-        <v>0.48</v>
-      </c>
-      <c r="G5" s="8">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="41.25" customHeight="1">
-      <c r="A6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="7">
-        <v>0.59</v>
-      </c>
-      <c r="D6" s="7">
-        <v>0.45</v>
-      </c>
-      <c r="E6" s="7">
-        <v>0.73</v>
-      </c>
-      <c r="F6" s="7">
-        <v>0.31</v>
-      </c>
-      <c r="G6" s="7">
-        <v>0.74</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="27.75" customHeight="1">
-      <c r="A7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="8">
+      <c r="H6" s="24">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="36" customHeight="1">
+      <c r="A7" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="D7" s="27">
+        <v>0.67</v>
+      </c>
+      <c r="E7" s="27">
+        <v>0.67</v>
+      </c>
+      <c r="F7" s="24">
+        <v>0.81</v>
+      </c>
+      <c r="G7" s="27">
         <v>0.39</v>
       </c>
-      <c r="D7" s="8">
-        <v>0.4</v>
-      </c>
-      <c r="E7" s="8">
-        <v>0.72</v>
-      </c>
-      <c r="F7" s="8">
-        <v>0.54</v>
-      </c>
-      <c r="G7" s="8">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="41.25" customHeight="1">
-      <c r="A8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="8">
-        <v>0.72</v>
-      </c>
-      <c r="D8" s="8">
-        <v>0.4</v>
-      </c>
-      <c r="E8" s="8">
-        <v>0.89</v>
-      </c>
-      <c r="F8" s="8">
-        <v>0.4</v>
-      </c>
-      <c r="G8" s="8">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="27.75" customHeight="1">
-      <c r="A9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="8">
-        <v>0.42</v>
-      </c>
-      <c r="D9" s="8">
-        <v>0.4</v>
-      </c>
-      <c r="E9" s="8">
-        <v>0.74</v>
-      </c>
-      <c r="F9" s="8">
-        <v>0.43</v>
-      </c>
-      <c r="G9" s="8">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="41.25" customHeight="1">
-      <c r="A10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="8">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="D10" s="8">
-        <v>0.35</v>
-      </c>
-      <c r="E10" s="8">
-        <v>0.93</v>
-      </c>
-      <c r="F10" s="8">
-        <v>0.37</v>
-      </c>
-      <c r="G10" s="8">
-        <v>0.73</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="27.75" customHeight="1">
-      <c r="A11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="8">
-        <v>0.67</v>
-      </c>
-      <c r="D11" s="8">
-        <v>0.67</v>
-      </c>
-      <c r="E11" s="8">
-        <v>0.81</v>
-      </c>
-      <c r="F11" s="8">
-        <v>0.39</v>
-      </c>
-      <c r="G11" s="8">
+      <c r="H7" s="27">
         <v>0.68</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="41.25" customHeight="1">
-      <c r="A12" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="8">
-        <v>0.74</v>
-      </c>
-      <c r="D12" s="8">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="E12" s="8">
-        <v>0.9</v>
-      </c>
-      <c r="F12" s="8">
-        <v>0.37</v>
-      </c>
-      <c r="G12" s="8">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="16.5" hidden="1" customHeight="1"/>
-    <row r="14" spans="1:7" ht="16.5" hidden="1" customHeight="1">
-      <c r="A14" s="29" t="s">
+    <row r="8" spans="1:8" ht="16.5" hidden="1" customHeight="1">
+      <c r="A8" s="29"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+    </row>
+    <row r="9" spans="1:8" ht="16.5" hidden="1" customHeight="1">
+      <c r="A9" s="39" t="s">
         <v>29</v>
       </c>
+      <c r="B9" s="39"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="40"/>
+    </row>
+    <row r="10" spans="1:8" ht="40.5" hidden="1" customHeight="1">
+      <c r="A10" s="40"/>
+      <c r="B10" s="40"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
+    </row>
+    <row r="11" spans="1:8" ht="139.5" hidden="1" customHeight="1">
+      <c r="A11" s="40"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="40"/>
+    </row>
+    <row r="12" spans="1:8" ht="16.5" hidden="1" customHeight="1">
+      <c r="A12" s="29"/>
+      <c r="B12" s="29"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="29"/>
+      <c r="H12" s="29"/>
+    </row>
+    <row r="13" spans="1:8" ht="16.5" customHeight="1">
+      <c r="A13" s="29"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="29"/>
+      <c r="H13" s="29"/>
+    </row>
+    <row r="14" spans="1:8" ht="16" customHeight="1">
+      <c r="A14" s="30"/>
       <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
       <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
+      <c r="F14" s="29"/>
       <c r="G14" s="30"/>
-    </row>
-    <row r="15" spans="1:7" ht="40.5" hidden="1" customHeight="1">
-      <c r="A15" s="30"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-    </row>
-    <row r="16" spans="1:7" ht="139.5" hidden="1" customHeight="1">
-      <c r="A16" s="30"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-    </row>
-    <row r="17" spans="1:6" ht="16.5" hidden="1" customHeight="1"/>
-    <row r="19" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="F19" s="5"/>
-    </row>
-    <row r="25" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A25" s="5"/>
-      <c r="D25" s="5"/>
+      <c r="H14" s="29"/>
+    </row>
+    <row r="15" spans="1:8" ht="16.5" customHeight="1">
+      <c r="A15" s="29"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+    </row>
+    <row r="16" spans="1:8" ht="16.5" customHeight="1">
+      <c r="A16" s="29"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="29"/>
+    </row>
+    <row r="17" spans="1:8" ht="16.5" customHeight="1">
+      <c r="A17" s="29"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="29"/>
+    </row>
+    <row r="18" spans="1:8" ht="16.5" customHeight="1">
+      <c r="A18" s="29"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
+    </row>
+    <row r="19" spans="1:8" ht="16.5" customHeight="1">
+      <c r="A19" s="29"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
+    </row>
+    <row r="20" spans="1:8" ht="16.5" customHeight="1">
+      <c r="A20" s="30"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
+    </row>
+    <row r="21" spans="1:8" ht="16.5" customHeight="1">
+      <c r="A21" s="29"/>
+      <c r="B21" s="29"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="29"/>
+      <c r="H21" s="29"/>
+    </row>
+    <row r="22" spans="1:8" ht="16.5" customHeight="1">
+      <c r="A22" s="29"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="29"/>
+      <c r="H22" s="29"/>
+    </row>
+    <row r="23" spans="1:8" ht="16.5" customHeight="1">
+      <c r="A23" s="29"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="29"/>
+    </row>
+    <row r="24" spans="1:8" ht="16.5" customHeight="1">
+      <c r="A24" s="29"/>
+      <c r="B24" s="29"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="29"/>
+      <c r="H24" s="29"/>
+    </row>
+    <row r="25" spans="1:8" ht="16.5" customHeight="1">
+      <c r="A25" s="29"/>
+      <c r="B25" s="29"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
+    </row>
+    <row r="26" spans="1:8" ht="16.5" customHeight="1">
+      <c r="A26" s="29"/>
+      <c r="B26" s="29"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="29"/>
+      <c r="H26" s="29"/>
+    </row>
+    <row r="27" spans="1:8" ht="16.5" customHeight="1">
+      <c r="A27" s="29"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29"/>
+    </row>
+    <row r="28" spans="1:8" ht="16.5" customHeight="1">
+      <c r="A28" s="29"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A14:G16"/>
+    <mergeCell ref="A9:H11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C2:C12">
-    <cfRule type="cellIs" dxfId="19" priority="9" operator="lessThan">
+  <conditionalFormatting sqref="C23">
+    <cfRule type="cellIs" dxfId="16" priority="6" operator="lessThan">
+      <formula>0.41</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="15" priority="7" operator="greaterThan">
+      <formula>0.41</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C23:G23">
+    <cfRule type="dataBar" priority="8">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFF89671"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{2A2C9AB1-94A0-8E4B-AE6D-F7120EE1AF90}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D7">
+    <cfRule type="cellIs" dxfId="14" priority="21" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="10" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="20" operator="lessThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:G12">
-    <cfRule type="dataBar" priority="23">
+  <conditionalFormatting sqref="D23">
+    <cfRule type="cellIs" dxfId="12" priority="4" operator="lessThan">
+      <formula>0.6</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="11" priority="5" operator="greaterThan">
+      <formula>0.6</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:H7">
+    <cfRule type="dataBar" priority="295">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCDA7B"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{8408B616-7BE3-61C4-DDE0-353DAA620AD8}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="9">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFF89671"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{315EC0EC-5A35-D04E-BEDE-551A03AA257E}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="10">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{34FE8147-C787-DA46-843A-DCFFBF513DBD}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="11">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{03E9FE6D-6943-4634-EB99-A9C46F46A4B3}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="300">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFBAC6F8"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{49738EA0-E9A9-0BFA-AFCA-021865618356}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="299">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -2236,11 +4396,59 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{03E9FE6D-6943-4634-EB99-A9C46F46A4B3}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="24">
+          <x14:id>{DD520DEA-27EE-2F62-A31D-01D156754911}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="298">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF7DDFE7"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{457321EA-D9F9-5DC8-6014-13B14F4135DC}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="297">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFDFB9EB"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{BB314B89-A913-9C79-F6F1-1038EFF476B9}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="296">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF7BE5BB"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{867C942A-D2A7-0AA6-F893-1F62E954D4F3}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="301">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCDA7B"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{3C08C0DB-23F8-44DB-C19F-0DA80D04FC55}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="291">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -2252,7 +4460,7 @@
         </ext>
       </extLst>
     </cfRule>
-    <cfRule type="dataBar" priority="25">
+    <cfRule type="dataBar" priority="292">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -2264,7 +4472,7 @@
         </ext>
       </extLst>
     </cfRule>
-    <cfRule type="dataBar" priority="26">
+    <cfRule type="dataBar" priority="293">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -2276,7 +4484,7 @@
         </ext>
       </extLst>
     </cfRule>
-    <cfRule type="dataBar" priority="27">
+    <cfRule type="dataBar" priority="294">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -2288,129 +4496,152 @@
         </ext>
       </extLst>
     </cfRule>
-    <cfRule type="dataBar" priority="28">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFCDA7B"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8408B616-7BE3-61C4-DDE0-353DAA620AD8}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="29">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF7BE5BB"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{867C942A-D2A7-0AA6-F893-1F62E954D4F3}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="30">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFDFB9EB"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{BB314B89-A913-9C79-F6F1-1038EFF476B9}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="31">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF7DDFE7"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{457321EA-D9F9-5DC8-6014-13B14F4135DC}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="32">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFF99570"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{DD520DEA-27EE-2F62-A31D-01D156754911}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="33">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFBAC6F8"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{49738EA0-E9A9-0BFA-AFCA-021865618356}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="34">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFCDA7B"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3C08C0DB-23F8-44DB-C19F-0DA80D04FC55}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D12">
-    <cfRule type="cellIs" dxfId="17" priority="7" operator="lessThan">
+  <conditionalFormatting sqref="E2:E7">
+    <cfRule type="cellIs" dxfId="10" priority="18" operator="lessThan">
       <formula>0.43</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="19" operator="greaterThan">
       <formula>0.43</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E12">
-    <cfRule type="cellIs" dxfId="15" priority="5" operator="lessThan">
+  <conditionalFormatting sqref="E23">
+    <cfRule type="cellIs" dxfId="8" priority="3" stopIfTrue="1" operator="greaterThan">
+      <formula>0.88</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="2" stopIfTrue="1" operator="lessThan">
+      <formula>0.88</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F7">
+    <cfRule type="cellIs" dxfId="6" priority="17" operator="greaterThan">
       <formula>0.72</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="16" operator="lessThan">
       <formula>0.72</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F12">
-    <cfRule type="cellIs" dxfId="13" priority="3" operator="lessThan">
+  <conditionalFormatting sqref="F23">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="greaterThan">
+      <formula>0.55</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G7">
+    <cfRule type="cellIs" dxfId="3" priority="15" operator="greaterThan">
       <formula>0.48</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="14" operator="lessThan">
       <formula>0.48</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G12">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="H2:H7">
+    <cfRule type="cellIs" dxfId="1" priority="13" operator="greaterThan">
       <formula>0.65</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="12" operator="lessThan">
       <formula>0.65</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{2A2C9AB1-94A0-8E4B-AE6D-F7120EE1AF90}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor theme="9"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>C23:G23</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{8408B616-7BE3-61C4-DDE0-353DAA620AD8}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{315EC0EC-5A35-D04E-BEDE-551A03AA257E}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{34FE8147-C787-DA46-843A-DCFFBF513DBD}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
           <x14:cfRule type="dataBar" id="{03E9FE6D-6943-4634-EB99-A9C46F46A4B3}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF63C384"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:negativeBorderColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{49738EA0-E9A9-0BFA-AFCA-021865618356}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{DD520DEA-27EE-2F62-A31D-01D156754911}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{457321EA-D9F9-5DC8-6014-13B14F4135DC}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{BB314B89-A913-9C79-F6F1-1038EFF476B9}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{867C942A-D2A7-0AA6-F893-1F62E954D4F3}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{3C08C0DB-23F8-44DB-C19F-0DA80D04FC55}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -2450,63 +4681,7 @@
               <x14:axisColor auto="1"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8408B616-7BE3-61C4-DDE0-353DAA620AD8}">
-            <x14:dataBar minLength="0" maxLength="100">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFF97885"/>
-              <x14:axisColor auto="1"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{867C942A-D2A7-0AA6-F893-1F62E954D4F3}">
-            <x14:dataBar minLength="0" maxLength="100">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFF97885"/>
-              <x14:axisColor auto="1"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{BB314B89-A913-9C79-F6F1-1038EFF476B9}">
-            <x14:dataBar minLength="0" maxLength="100">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFF97885"/>
-              <x14:axisColor auto="1"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{457321EA-D9F9-5DC8-6014-13B14F4135DC}">
-            <x14:dataBar minLength="0" maxLength="100">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFF97885"/>
-              <x14:axisColor auto="1"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{DD520DEA-27EE-2F62-A31D-01D156754911}">
-            <x14:dataBar minLength="0" maxLength="100">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFF97885"/>
-              <x14:axisColor auto="1"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{49738EA0-E9A9-0BFA-AFCA-021865618356}">
-            <x14:dataBar minLength="0" maxLength="100">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFF97885"/>
-              <x14:axisColor auto="1"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3C08C0DB-23F8-44DB-C19F-0DA80D04FC55}">
-            <x14:dataBar minLength="0" maxLength="100">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFF97885"/>
-              <x14:axisColor auto="1"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>C2:G12</xm:sqref>
+          <xm:sqref>D2:H7</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -2514,7 +4689,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05C95AD9-F5AD-AD45-B7D5-91BD34E1D447}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -2532,26 +4707,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="30"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="38"/>
     </row>
     <row r="2" spans="1:7" ht="16.5" customHeight="1">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
     </row>
     <row r="3" spans="1:7" ht="16.5" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -2581,22 +4756,22 @@
       <c r="E7" s="5"/>
     </row>
     <row r="8" spans="1:7" ht="16.5" customHeight="1">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="30"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="30"/>
+      <c r="B8" s="38"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="38"/>
     </row>
     <row r="9" spans="1:7" ht="16.5" customHeight="1">
-      <c r="A9" s="32" t="s">
+      <c r="A9" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="32"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
     </row>
     <row r="10" spans="1:7" ht="16.5" customHeight="1">
       <c r="A10" s="1" t="s">
@@ -2614,16 +4789,16 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="16.5" customHeight="1">
-      <c r="A14" s="31" t="s">
+      <c r="A14" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="B14" s="30"/>
+      <c r="B14" s="38"/>
     </row>
     <row r="15" spans="1:7" ht="16.5" customHeight="1">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="32"/>
+      <c r="B15" s="42"/>
     </row>
     <row r="16" spans="1:7" ht="16.5" customHeight="1">
       <c r="A16" s="1" t="s">
@@ -2646,16 +4821,16 @@
       </c>
     </row>
     <row r="21" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A21" s="31" t="s">
+      <c r="A21" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="B21" s="30"/>
+      <c r="B21" s="38"/>
     </row>
     <row r="22" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A22" s="32" t="s">
+      <c r="A22" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="32"/>
+      <c r="B22" s="42"/>
     </row>
     <row r="23" spans="1:2" ht="16.5" customHeight="1">
       <c r="A23" s="1" t="s">
@@ -2678,16 +4853,16 @@
       </c>
     </row>
     <row r="28" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A28" s="31" t="s">
+      <c r="A28" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="B28" s="30"/>
+      <c r="B28" s="38"/>
     </row>
     <row r="29" spans="1:2" ht="16.5" customHeight="1">
-      <c r="A29" s="32" t="s">
+      <c r="A29" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="B29" s="32"/>
+      <c r="B29" s="42"/>
     </row>
     <row r="30" spans="1:2" ht="16.5" customHeight="1">
       <c r="A30" s="1" t="s">
@@ -2711,11 +4886,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="F2:G2"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -2727,6 +4897,11 @@
     <mergeCell ref="D9:E9"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:E2"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="F2:G2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/app/data/RAG 系统评估指标结果.xlsx
+++ b/src/app/data/RAG 系统评估指标结果.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/laixiangran/lai-workspace/ai-learn/src/app/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E691E599-0B59-E24C-9C58-3323D1C9DDCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A23C540-CB69-714E-BD56-4B7FF84EB0D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="1" xr2:uid="{752BAC88-3D22-6345-9E5D-6A586CA68B77}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="99">
   <si>
     <t>版本</t>
   </si>
@@ -424,18 +424,12 @@
     <t>2. 根据每个上下文片段的得分，计算上下文相关性。</t>
   </si>
   <si>
-    <t>一句话总结：答案忠实度越高，LLM 出现幻觉的概率越低。</t>
-  </si>
-  <si>
     <t>1. 将实际答案拆分成多个关键信息；</t>
   </si>
   <si>
     <t>3. 根据每个关键信息的得分，计算答案忠实度。</t>
   </si>
   <si>
-    <t>一句话总结：答案相关性越高，实际答案冗余或跑题越少。</t>
-  </si>
-  <si>
     <t>1. 根据实际答案推导出多个模拟问题；</t>
   </si>
   <si>
@@ -443,9 +437,6 @@
   </si>
   <si>
     <t>3. 根据每个模拟问题的得分，计算答案相关性。</t>
-  </si>
-  <si>
-    <t>一句话总结：答案正确性越高，实际答案越准确。</t>
   </si>
   <si>
     <t>2. 逐个分析每个关键信息是否可归因于给定的实际答案；</t>
@@ -694,11 +685,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>切分方法：将每个文档块的模拟问题单独向量化，将基于模拟问题检索到的文档块 和 v5.3 检索到的文档块进行合并</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>切分方法：将每个文档块的模拟问题单独向量化，并基于模拟问题检索相应文档块</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一句话总结：答案忠实度越高，LLM 回答出现幻觉的概率越低。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一句话总结：答案相关性越高，LLM 回答冗余或跑题越少。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一句话总结：答案正确性越高，LLM 回答越准确。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1081,11 +1080,6 @@
   <dxfs count="47">
     <dxf>
       <font>
-        <color rgb="FF00B14D"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FFFE0300"/>
       </font>
     </dxf>
@@ -1101,22 +1095,7 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF00B14D"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFE0300"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
       </font>
     </dxf>
     <dxf>
@@ -1146,12 +1125,32 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFFE0300"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF00B14D"/>
       </font>
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FFFE0300"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B14D"/>
       </font>
     </dxf>
     <dxf>
@@ -1266,22 +1265,12 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF00B14D"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FFFE0300"/>
       </font>
     </dxf>
     <dxf>
       <font>
         <color rgb="FF00B14D"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFE0300"/>
       </font>
     </dxf>
     <dxf>
@@ -1306,12 +1295,22 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFFE0300"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF00B14D"/>
       </font>
     </dxf>
     <dxf>
       <font>
         <color rgb="FFFE0300"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B14D"/>
       </font>
     </dxf>
   </dxfs>
@@ -1651,7 +1650,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>2</v>
@@ -1660,7 +1659,7 @@
         <v>3</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>5</v>
@@ -1674,7 +1673,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D3" s="20"/>
       <c r="E3" s="8">
@@ -1695,13 +1694,13 @@
     </row>
     <row r="4" spans="2:9" ht="33" customHeight="1">
       <c r="B4" s="31" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C4" s="34" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E4" s="8">
         <v>0.23</v>
@@ -1723,7 +1722,7 @@
       <c r="B5" s="32"/>
       <c r="C5" s="35"/>
       <c r="D5" s="22" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E5" s="8">
         <v>0.34</v>
@@ -1745,7 +1744,7 @@
       <c r="B6" s="32"/>
       <c r="C6" s="35"/>
       <c r="D6" s="19" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E6" s="8">
         <v>0.4</v>
@@ -1767,7 +1766,7 @@
       <c r="B7" s="32"/>
       <c r="C7" s="35"/>
       <c r="D7" s="22" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E7" s="8">
         <v>0.42</v>
@@ -1789,7 +1788,7 @@
       <c r="B8" s="32"/>
       <c r="C8" s="35"/>
       <c r="D8" s="22" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E8" s="8">
         <v>0.43</v>
@@ -1811,7 +1810,7 @@
       <c r="B9" s="32"/>
       <c r="C9" s="35"/>
       <c r="D9" s="22" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E9" s="8">
         <v>0.52</v>
@@ -1833,7 +1832,7 @@
       <c r="B10" s="32"/>
       <c r="C10" s="35"/>
       <c r="D10" s="22" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E10" s="8">
         <v>0.56000000000000005</v>
@@ -1855,7 +1854,7 @@
       <c r="B11" s="32"/>
       <c r="C11" s="35"/>
       <c r="D11" s="22" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E11" s="8">
         <v>0.52</v>
@@ -1877,7 +1876,7 @@
       <c r="B12" s="33"/>
       <c r="C12" s="36"/>
       <c r="D12" s="22" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E12" s="8">
         <v>0.54</v>
@@ -1897,13 +1896,13 @@
     </row>
     <row r="13" spans="2:9" ht="46" customHeight="1">
       <c r="B13" s="31" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
@@ -1915,7 +1914,7 @@
       <c r="B14" s="32"/>
       <c r="C14" s="35"/>
       <c r="D14" s="22" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F14" s="8"/>
       <c r="G14" s="8"/>
@@ -1926,7 +1925,7 @@
       <c r="B15" s="32"/>
       <c r="C15" s="35"/>
       <c r="D15" s="19" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
@@ -1938,7 +1937,7 @@
       <c r="B16" s="32"/>
       <c r="C16" s="35"/>
       <c r="D16" s="22" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
@@ -1950,7 +1949,7 @@
       <c r="B17" s="32"/>
       <c r="C17" s="35"/>
       <c r="D17" s="22" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E17" s="8"/>
       <c r="F17" s="8"/>
@@ -1962,7 +1961,7 @@
       <c r="B18" s="32"/>
       <c r="C18" s="35"/>
       <c r="D18" s="22" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E18" s="8">
         <v>0.52</v>
@@ -1984,7 +1983,7 @@
       <c r="B19" s="32"/>
       <c r="C19" s="35"/>
       <c r="D19" s="22" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
@@ -1996,7 +1995,7 @@
       <c r="B20" s="32"/>
       <c r="C20" s="35"/>
       <c r="D20" s="22" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
@@ -2008,7 +2007,7 @@
       <c r="B21" s="33"/>
       <c r="C21" s="36"/>
       <c r="D21" s="22" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
@@ -2018,13 +2017,13 @@
     </row>
     <row r="22" spans="2:9" ht="46" customHeight="1">
       <c r="B22" s="31" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C22" s="34" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
@@ -2036,7 +2035,7 @@
       <c r="B23" s="32"/>
       <c r="C23" s="35"/>
       <c r="D23" s="22" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F23" s="8"/>
       <c r="G23" s="8"/>
@@ -2047,7 +2046,7 @@
       <c r="B24" s="32"/>
       <c r="C24" s="35"/>
       <c r="D24" s="19" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E24" s="8"/>
       <c r="F24" s="8"/>
@@ -2059,7 +2058,7 @@
       <c r="B25" s="32"/>
       <c r="C25" s="35"/>
       <c r="D25" s="22" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
@@ -2071,7 +2070,7 @@
       <c r="B26" s="32"/>
       <c r="C26" s="35"/>
       <c r="D26" s="22" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
@@ -2083,7 +2082,7 @@
       <c r="B27" s="32"/>
       <c r="C27" s="35"/>
       <c r="D27" s="22" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E27" s="8">
         <v>0.49</v>
@@ -2105,7 +2104,7 @@
       <c r="B28" s="32"/>
       <c r="C28" s="35"/>
       <c r="D28" s="22" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E28" s="8"/>
       <c r="F28" s="8"/>
@@ -2117,7 +2116,7 @@
       <c r="B29" s="32"/>
       <c r="C29" s="35"/>
       <c r="D29" s="22" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E29" s="8"/>
       <c r="F29" s="8"/>
@@ -2129,7 +2128,7 @@
       <c r="B30" s="33"/>
       <c r="C30" s="36"/>
       <c r="D30" s="22" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E30" s="8"/>
       <c r="F30" s="8"/>
@@ -2148,14 +2147,26 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E3:E13 E15:E22 E24:E30">
-    <cfRule type="cellIs" dxfId="46" priority="35" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="46" priority="34" operator="lessThan">
       <formula>0.5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="34" operator="lessThan">
+    <cfRule type="cellIs" dxfId="45" priority="35" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:I5">
+    <cfRule type="dataBar" priority="14">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFF99570"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{25477AA2-18BD-EE45-A477-DC593098217D}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
     <cfRule type="dataBar" priority="15">
       <dataBar>
         <cfvo type="min"/>
@@ -2168,6 +2179,114 @@
         </ext>
       </extLst>
     </cfRule>
+    <cfRule type="dataBar" priority="16">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFF99570"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{F449C4A6-8AC2-5140-A907-64794CF7A6B7}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="17">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFF99570"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{F8CE1320-0FAA-DF45-AE75-6521D1216F35}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="18">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFBAC6F8"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{B3467C43-1D33-AB48-8695-AD81DD88C417}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="19">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCDA7B"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{F01E47F2-89F1-C444-AB7E-42F801B4962C}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="20">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF7BE5BB"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{0696D2A9-42CA-7246-AA3E-73F17C16E754}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="21">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFDFB9EB"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{57EE048F-379B-774D-875C-2ED515DC452C}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="22">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF7DDFE7"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{6BE560D1-02B8-3741-957B-148E4955A767}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="23">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFF99570"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{19CC04DE-B1FE-5841-B6E6-3DDBD3D44E58}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="24">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFBAC6F8"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{BDC52813-7112-3B4E-ABCA-9D2846FB4236}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
     <cfRule type="dataBar" priority="25">
       <dataBar>
         <cfvo type="min"/>
@@ -2177,126 +2296,6 @@
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
           <x14:id>{DD571C54-5F9F-924D-BAA5-39A08A609054}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="24">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFBAC6F8"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{BDC52813-7112-3B4E-ABCA-9D2846FB4236}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="23">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFF99570"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{19CC04DE-B1FE-5841-B6E6-3DDBD3D44E58}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="22">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF7DDFE7"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6BE560D1-02B8-3741-957B-148E4955A767}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="21">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFDFB9EB"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{57EE048F-379B-774D-875C-2ED515DC452C}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="20">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF7BE5BB"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0696D2A9-42CA-7246-AA3E-73F17C16E754}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="19">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFCDA7B"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{F01E47F2-89F1-C444-AB7E-42F801B4962C}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="18">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFBAC6F8"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{B3467C43-1D33-AB48-8695-AD81DD88C417}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="17">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFF99570"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{F8CE1320-0FAA-DF45-AE75-6521D1216F35}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="16">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFF99570"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{F449C4A6-8AC2-5140-A907-64794CF7A6B7}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="14">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFF99570"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{25477AA2-18BD-EE45-A477-DC593098217D}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -2310,6 +2309,126 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5">
+    <cfRule type="dataBar" priority="3">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFBAC6F8"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{C4A3FB4A-FF8F-1345-B8F6-9183523E6A79}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="4">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFF99570"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{465D0531-80C6-1842-9069-B81E151316FA}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="5">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFF99570"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{75484FA4-C3AC-0B47-969B-E9915DB46D14}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="6">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFBAC6F8"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{C515C054-BD10-8343-8F8A-65C7651AE4BF}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="7">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCDA7B"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{E71D8BC7-AD9A-9C49-9D75-8CEB348BE1EA}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="8">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF7BE5BB"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{243A9755-04D9-AD48-A83E-D1E1DD2D8801}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="9">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFDFB9EB"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{1EAFA712-8BB4-F84F-8ABC-9FC881958D4A}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="10">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF7DDFE7"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{8068B1DA-7D22-214C-8D0D-76243CCA2A5C}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="11">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFF99570"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{D4C67D78-9145-5D40-9AD9-AE95FF79EF24}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="12">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFBAC6F8"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{DDA361B5-2ABE-6B41-8AA7-861D28E0CA2C}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
     <cfRule type="dataBar" priority="13">
       <dataBar>
         <cfvo type="min"/>
@@ -2319,126 +2438,6 @@
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
           <x14:id>{245237B8-ED1D-1044-AC4A-109EAEFA1808}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="12">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFBAC6F8"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{DDA361B5-2ABE-6B41-8AA7-861D28E0CA2C}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="11">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFF99570"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{D4C67D78-9145-5D40-9AD9-AE95FF79EF24}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="10">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF7DDFE7"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8068B1DA-7D22-214C-8D0D-76243CCA2A5C}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="9">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFDFB9EB"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1EAFA712-8BB4-F84F-8ABC-9FC881958D4A}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="8">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF7BE5BB"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{243A9755-04D9-AD48-A83E-D1E1DD2D8801}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="7">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFCDA7B"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{E71D8BC7-AD9A-9C49-9D75-8CEB348BE1EA}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="6">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFBAC6F8"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{C515C054-BD10-8343-8F8A-65C7651AE4BF}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="5">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFF99570"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{75484FA4-C3AC-0B47-969B-E9915DB46D14}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="4">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFF99570"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{465D0531-80C6-1842-9069-B81E151316FA}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="3">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFBAC6F8"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{C4A3FB4A-FF8F-1345-B8F6-9183523E6A79}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -2624,18 +2623,18 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H30">
-    <cfRule type="cellIs" dxfId="40" priority="29" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="40" priority="28" operator="lessThan">
       <formula>0.48</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="28" operator="lessThan">
+    <cfRule type="cellIs" dxfId="39" priority="29" operator="greaterThan">
       <formula>0.48</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3:I30">
-    <cfRule type="cellIs" dxfId="38" priority="27" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="38" priority="26" operator="lessThan">
       <formula>0.65</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="26" operator="lessThan">
+    <cfRule type="cellIs" dxfId="37" priority="27" operator="greaterThan">
       <formula>0.65</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2645,6 +2644,14 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{25477AA2-18BD-EE45-A477-DC593098217D}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
           <x14:cfRule type="dataBar" id="{799AA421-9FAE-9540-9F66-7829C866154A}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
@@ -2653,78 +2660,6 @@
               <x14:axisColor auto="1"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{DD571C54-5F9F-924D-BAA5-39A08A609054}">
-            <x14:dataBar minLength="0" maxLength="100">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFF97885"/>
-              <x14:axisColor auto="1"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{BDC52813-7112-3B4E-ABCA-9D2846FB4236}">
-            <x14:dataBar minLength="0" maxLength="100">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFF97885"/>
-              <x14:axisColor auto="1"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{19CC04DE-B1FE-5841-B6E6-3DDBD3D44E58}">
-            <x14:dataBar minLength="0" maxLength="100">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFF97885"/>
-              <x14:axisColor auto="1"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6BE560D1-02B8-3741-957B-148E4955A767}">
-            <x14:dataBar minLength="0" maxLength="100">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFF97885"/>
-              <x14:axisColor auto="1"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{57EE048F-379B-774D-875C-2ED515DC452C}">
-            <x14:dataBar minLength="0" maxLength="100">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFF97885"/>
-              <x14:axisColor auto="1"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0696D2A9-42CA-7246-AA3E-73F17C16E754}">
-            <x14:dataBar minLength="0" maxLength="100">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFF97885"/>
-              <x14:axisColor auto="1"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{F01E47F2-89F1-C444-AB7E-42F801B4962C}">
-            <x14:dataBar minLength="0" maxLength="100">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFF97885"/>
-              <x14:axisColor auto="1"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{B3467C43-1D33-AB48-8695-AD81DD88C417}">
-            <x14:dataBar minLength="0" maxLength="100">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFF97885"/>
-              <x14:axisColor auto="1"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{F8CE1320-0FAA-DF45-AE75-6521D1216F35}">
-            <x14:dataBar minLength="0" maxLength="100">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFF97885"/>
-              <x14:axisColor auto="1"/>
-            </x14:dataBar>
-          </x14:cfRule>
           <x14:cfRule type="dataBar" id="{F449C4A6-8AC2-5140-A907-64794CF7A6B7}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
@@ -2733,7 +2668,71 @@
               <x14:axisColor auto="1"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{25477AA2-18BD-EE45-A477-DC593098217D}">
+          <x14:cfRule type="dataBar" id="{F8CE1320-0FAA-DF45-AE75-6521D1216F35}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{B3467C43-1D33-AB48-8695-AD81DD88C417}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{F01E47F2-89F1-C444-AB7E-42F801B4962C}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{0696D2A9-42CA-7246-AA3E-73F17C16E754}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{57EE048F-379B-774D-875C-2ED515DC452C}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{6BE560D1-02B8-3741-957B-148E4955A767}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{19CC04DE-B1FE-5841-B6E6-3DDBD3D44E58}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{BDC52813-7112-3B4E-ABCA-9D2846FB4236}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{DD571C54-5F9F-924D-BAA5-39A08A609054}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -2744,72 +2743,8 @@
           <xm:sqref>E5:I5</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{245237B8-ED1D-1044-AC4A-109EAEFA1808}">
-            <x14:dataBar minLength="0" maxLength="100">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFF97885"/>
-              <x14:axisColor auto="1"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{DDA361B5-2ABE-6B41-8AA7-861D28E0CA2C}">
-            <x14:dataBar minLength="0" maxLength="100">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFF97885"/>
-              <x14:axisColor auto="1"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{D4C67D78-9145-5D40-9AD9-AE95FF79EF24}">
-            <x14:dataBar minLength="0" maxLength="100">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFF97885"/>
-              <x14:axisColor auto="1"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8068B1DA-7D22-214C-8D0D-76243CCA2A5C}">
-            <x14:dataBar minLength="0" maxLength="100">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFF97885"/>
-              <x14:axisColor auto="1"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{1EAFA712-8BB4-F84F-8ABC-9FC881958D4A}">
-            <x14:dataBar minLength="0" maxLength="100">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFF97885"/>
-              <x14:axisColor auto="1"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{243A9755-04D9-AD48-A83E-D1E1DD2D8801}">
-            <x14:dataBar minLength="0" maxLength="100">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFF97885"/>
-              <x14:axisColor auto="1"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{E71D8BC7-AD9A-9C49-9D75-8CEB348BE1EA}">
-            <x14:dataBar minLength="0" maxLength="100">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFF97885"/>
-              <x14:axisColor auto="1"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{C515C054-BD10-8343-8F8A-65C7651AE4BF}">
-            <x14:dataBar minLength="0" maxLength="100">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFF97885"/>
-              <x14:axisColor auto="1"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{75484FA4-C3AC-0B47-969B-E9915DB46D14}">
-            <x14:dataBar minLength="0" maxLength="100">
+          <x14:cfRule type="dataBar" id="{C4A3FB4A-FF8F-1345-B8F6-9183523E6A79}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
               <x14:negativeFillColor rgb="FFF97885"/>
@@ -2824,8 +2759,72 @@
               <x14:axisColor auto="1"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{C4A3FB4A-FF8F-1345-B8F6-9183523E6A79}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+          <x14:cfRule type="dataBar" id="{75484FA4-C3AC-0B47-969B-E9915DB46D14}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{C515C054-BD10-8343-8F8A-65C7651AE4BF}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{E71D8BC7-AD9A-9C49-9D75-8CEB348BE1EA}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{243A9755-04D9-AD48-A83E-D1E1DD2D8801}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{1EAFA712-8BB4-F84F-8ABC-9FC881958D4A}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{8068B1DA-7D22-214C-8D0D-76243CCA2A5C}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{D4C67D78-9145-5D40-9AD9-AE95FF79EF24}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{DDA361B5-2ABE-6B41-8AA7-861D28E0CA2C}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{245237B8-ED1D-1044-AC4A-109EAEFA1808}">
+            <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
               <x14:negativeFillColor rgb="FFF97885"/>
@@ -2967,14 +2966,14 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="B2:H9"/>
+  <dimension ref="B2:H8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="3.1640625" customWidth="1"/>
     <col min="2" max="2" width="6.83203125" customWidth="1"/>
     <col min="3" max="3" width="31.1640625" customWidth="1"/>
-    <col min="4" max="4" width="26.83203125" customWidth="1"/>
-    <col min="5" max="7" width="26.83203125" hidden="1" customWidth="1"/>
+    <col min="4" max="5" width="26.83203125" customWidth="1"/>
+    <col min="6" max="7" width="26.83203125" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="26.83203125" customWidth="1"/>
     <col min="9" max="9" width="26.1640625" customWidth="1"/>
   </cols>
@@ -2993,7 +2992,7 @@
         <v>3</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>5</v>
@@ -3004,10 +3003,10 @@
     </row>
     <row r="3" spans="2:8" ht="140" customHeight="1">
       <c r="B3" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D3" s="8">
         <v>0.41</v>
@@ -3027,10 +3026,10 @@
     </row>
     <row r="4" spans="2:8" ht="46" customHeight="1">
       <c r="B4" s="25" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D4" s="27">
         <v>0.44</v>
@@ -3050,10 +3049,10 @@
     </row>
     <row r="5" spans="2:8" ht="46" customHeight="1">
       <c r="B5" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" s="26" t="s">
         <v>90</v>
-      </c>
-      <c r="C5" s="26" t="s">
-        <v>93</v>
       </c>
       <c r="D5" s="27">
         <v>0.54</v>
@@ -3073,10 +3072,10 @@
     </row>
     <row r="6" spans="2:8" ht="58" customHeight="1">
       <c r="B6" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" s="26" t="s">
         <v>91</v>
-      </c>
-      <c r="C6" s="26" t="s">
-        <v>94</v>
       </c>
       <c r="D6" s="27">
         <v>0.56000000000000005</v>
@@ -3091,15 +3090,15 @@
         <v>0.66</v>
       </c>
       <c r="H6" s="27">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" ht="58" customHeight="1">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" ht="58" hidden="1" customHeight="1">
       <c r="B7" s="25" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D7" s="27">
         <v>0.52</v>
@@ -3117,12 +3116,12 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="58" customHeight="1">
+    <row r="8" spans="2:8" ht="58" hidden="1" customHeight="1">
       <c r="B8" s="25" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D8" s="27">
         <v>0.52</v>
@@ -3140,32 +3139,9 @@
         <v>0.48</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="58" customHeight="1">
-      <c r="B9" s="25" t="s">
-        <v>97</v>
-      </c>
-      <c r="C9" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="D9" s="27">
-        <v>0.65</v>
-      </c>
-      <c r="E9" s="27">
-        <v>0.51</v>
-      </c>
-      <c r="F9" s="27">
-        <v>0.82</v>
-      </c>
-      <c r="G9" s="27">
-        <v>0.23</v>
-      </c>
-      <c r="H9" s="27">
-        <v>0.59</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="D3:D9">
+  <conditionalFormatting sqref="D3:D8">
     <cfRule type="cellIs" dxfId="36" priority="19" operator="lessThan">
       <formula>0.41</formula>
     </cfRule>
@@ -3173,7 +3149,7 @@
       <formula>0.41</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D3:H13">
+  <conditionalFormatting sqref="D3:H12">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -3187,7 +3163,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3:E9">
+  <conditionalFormatting sqref="E3:E8">
     <cfRule type="cellIs" dxfId="34" priority="17" stopIfTrue="1" operator="lessThan">
       <formula>0.53</formula>
     </cfRule>
@@ -3195,7 +3171,7 @@
       <formula>0.53</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F9">
+  <conditionalFormatting sqref="F3:F8">
     <cfRule type="cellIs" dxfId="32" priority="15" stopIfTrue="1" operator="lessThan">
       <formula>0.84</formula>
     </cfRule>
@@ -3203,7 +3179,7 @@
       <formula>0.84</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3:G9">
+  <conditionalFormatting sqref="G3:G8">
     <cfRule type="cellIs" dxfId="30" priority="3" operator="lessThan">
       <formula>0.55</formula>
     </cfRule>
@@ -3211,7 +3187,7 @@
       <formula>0.55</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3:H9">
+  <conditionalFormatting sqref="H3:H8">
     <cfRule type="cellIs" dxfId="28" priority="4" operator="lessThan">
       <formula>0.48</formula>
     </cfRule>
@@ -3237,7 +3213,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>D3:H13</xm:sqref>
+          <xm:sqref>D3:H12</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -3895,10 +3871,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>2</v>
@@ -3921,10 +3897,10 @@
         <v>7</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D2" s="8">
         <v>0.5</v>
@@ -3947,10 +3923,10 @@
         <v>9</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D3" s="8">
         <v>0.36</v>
@@ -3973,10 +3949,10 @@
         <v>13</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D4" s="8">
         <v>0.5</v>
@@ -3999,10 +3975,10 @@
         <v>17</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D5" s="8">
         <v>0.39</v>
@@ -4022,13 +3998,13 @@
     </row>
     <row r="6" spans="1:8" ht="36" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D6" s="24">
         <v>0.42</v>
@@ -4048,13 +4024,13 @@
     </row>
     <row r="7" spans="1:8" ht="36" customHeight="1">
       <c r="A7" s="25" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D7" s="27">
         <v>0.67</v>
@@ -4312,10 +4288,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:D7">
-    <cfRule type="cellIs" dxfId="14" priority="21" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="20" operator="lessThan">
       <formula>0.5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="20" operator="lessThan">
+    <cfRule type="cellIs" dxfId="13" priority="21" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4328,18 +4304,6 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:H7">
-    <cfRule type="dataBar" priority="295">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFCDA7B"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8408B616-7BE3-61C4-DDE0-353DAA620AD8}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
     <cfRule type="dataBar" priority="9">
       <dataBar>
         <cfvo type="min"/>
@@ -4376,6 +4340,114 @@
         </ext>
       </extLst>
     </cfRule>
+    <cfRule type="dataBar" priority="291">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFBAC6F8"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{18D57835-054B-6A2E-61E7-378ED5B10DBE}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="292">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFF99570"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{0EDA5377-8A65-0B40-68CD-74F173EFB36E}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="293">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFF99570"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{623D622D-592C-A5D3-AE0E-3D153D4D6786}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="294">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFBAC6F8"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{81E6FFFE-ED50-9FF3-9741-33C64EDA10BE}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="295">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCDA7B"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{8408B616-7BE3-61C4-DDE0-353DAA620AD8}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="296">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF7BE5BB"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{867C942A-D2A7-0AA6-F893-1F62E954D4F3}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="297">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFDFB9EB"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{BB314B89-A913-9C79-F6F1-1038EFF476B9}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="298">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF7DDFE7"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{457321EA-D9F9-5DC8-6014-13B14F4135DC}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="299">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFF99570"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{DD520DEA-27EE-2F62-A31D-01D156754911}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
     <cfRule type="dataBar" priority="300">
       <dataBar>
         <cfvo type="min"/>
@@ -4388,54 +4460,6 @@
         </ext>
       </extLst>
     </cfRule>
-    <cfRule type="dataBar" priority="299">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFF99570"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{DD520DEA-27EE-2F62-A31D-01D156754911}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="298">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF7DDFE7"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{457321EA-D9F9-5DC8-6014-13B14F4135DC}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="297">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFDFB9EB"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{BB314B89-A913-9C79-F6F1-1038EFF476B9}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="296">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF7BE5BB"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{867C942A-D2A7-0AA6-F893-1F62E954D4F3}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
     <cfRule type="dataBar" priority="301">
       <dataBar>
         <cfvo type="min"/>
@@ -4445,54 +4469,6 @@
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
           <x14:id>{3C08C0DB-23F8-44DB-C19F-0DA80D04FC55}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="291">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFBAC6F8"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{18D57835-054B-6A2E-61E7-378ED5B10DBE}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="292">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFF99570"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0EDA5377-8A65-0B40-68CD-74F173EFB36E}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="293">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFF99570"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{623D622D-592C-A5D3-AE0E-3D153D4D6786}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="294">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFBAC6F8"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{81E6FFFE-ED50-9FF3-9741-33C64EDA10BE}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4506,18 +4482,18 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E23">
-    <cfRule type="cellIs" dxfId="8" priority="3" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="2" stopIfTrue="1" operator="lessThan">
       <formula>0.88</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="2" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="3" stopIfTrue="1" operator="greaterThan">
       <formula>0.88</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F7">
-    <cfRule type="cellIs" dxfId="6" priority="17" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="16" operator="lessThan">
       <formula>0.72</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="16" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="17" operator="greaterThan">
       <formula>0.72</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4527,18 +4503,18 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G7">
-    <cfRule type="cellIs" dxfId="3" priority="15" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="14" operator="lessThan">
       <formula>0.48</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="14" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="15" operator="greaterThan">
       <formula>0.48</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H7">
-    <cfRule type="cellIs" dxfId="1" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="12" operator="lessThan">
       <formula>0.65</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="12" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="13" operator="greaterThan">
       <formula>0.65</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4563,14 +4539,6 @@
           <xm:sqref>C23:G23</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8408B616-7BE3-61C4-DDE0-353DAA620AD8}">
-            <x14:dataBar minLength="0" maxLength="100">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFF97885"/>
-              <x14:axisColor auto="1"/>
-            </x14:dataBar>
-          </x14:cfRule>
           <x14:cfRule type="dataBar" id="{315EC0EC-5A35-D04E-BEDE-551A03AA257E}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
@@ -4601,54 +4569,6 @@
               <x14:axisColor auto="1"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{49738EA0-E9A9-0BFA-AFCA-021865618356}">
-            <x14:dataBar minLength="0" maxLength="100">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFF97885"/>
-              <x14:axisColor auto="1"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{DD520DEA-27EE-2F62-A31D-01D156754911}">
-            <x14:dataBar minLength="0" maxLength="100">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFF97885"/>
-              <x14:axisColor auto="1"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{457321EA-D9F9-5DC8-6014-13B14F4135DC}">
-            <x14:dataBar minLength="0" maxLength="100">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFF97885"/>
-              <x14:axisColor auto="1"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{BB314B89-A913-9C79-F6F1-1038EFF476B9}">
-            <x14:dataBar minLength="0" maxLength="100">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFF97885"/>
-              <x14:axisColor auto="1"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{867C942A-D2A7-0AA6-F893-1F62E954D4F3}">
-            <x14:dataBar minLength="0" maxLength="100">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFF97885"/>
-              <x14:axisColor auto="1"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3C08C0DB-23F8-44DB-C19F-0DA80D04FC55}">
-            <x14:dataBar minLength="0" maxLength="100">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:negativeFillColor rgb="FFF97885"/>
-              <x14:axisColor auto="1"/>
-            </x14:dataBar>
-          </x14:cfRule>
           <x14:cfRule type="dataBar" id="{18D57835-054B-6A2E-61E7-378ED5B10DBE}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0">
               <x14:cfvo type="autoMin"/>
@@ -4674,6 +4594,62 @@
             </x14:dataBar>
           </x14:cfRule>
           <x14:cfRule type="dataBar" id="{81E6FFFE-ED50-9FF3-9741-33C64EDA10BE}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{8408B616-7BE3-61C4-DDE0-353DAA620AD8}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{867C942A-D2A7-0AA6-F893-1F62E954D4F3}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{BB314B89-A913-9C79-F6F1-1038EFF476B9}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{457321EA-D9F9-5DC8-6014-13B14F4135DC}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{DD520DEA-27EE-2F62-A31D-01D156754911}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{49738EA0-E9A9-0BFA-AFCA-021865618356}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFF97885"/>
+              <x14:axisColor auto="1"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{3C08C0DB-23F8-44DB-C19F-0DA80D04FC55}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -4708,7 +4684,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1">
       <c r="A1" s="41" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B1" s="38"/>
       <c r="C1" s="38"/>
@@ -4757,7 +4733,7 @@
     </row>
     <row r="8" spans="1:7" ht="16.5" customHeight="1">
       <c r="A8" s="41" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B8" s="38"/>
       <c r="C8" s="38"/>
@@ -4790,13 +4766,13 @@
     </row>
     <row r="14" spans="1:7" ht="16.5" customHeight="1">
       <c r="A14" s="41" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B14" s="38"/>
     </row>
     <row r="15" spans="1:7" ht="16.5" customHeight="1">
       <c r="A15" s="42" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="B15" s="42"/>
     </row>
@@ -4807,7 +4783,7 @@
     </row>
     <row r="17" spans="1:2" ht="16.5" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="16.5" customHeight="1">
@@ -4817,18 +4793,18 @@
     </row>
     <row r="19" spans="1:2" ht="16.5" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="16.5" customHeight="1">
       <c r="A21" s="41" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B21" s="38"/>
     </row>
     <row r="22" spans="1:2" ht="16.5" customHeight="1">
       <c r="A22" s="42" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="B22" s="42"/>
     </row>
@@ -4839,28 +4815,28 @@
     </row>
     <row r="24" spans="1:2" ht="16.5" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="16.5" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="16.5" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="16.5" customHeight="1">
       <c r="A28" s="41" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B28" s="38"/>
     </row>
     <row r="29" spans="1:2" ht="16.5" customHeight="1">
       <c r="A29" s="42" t="s">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="B29" s="42"/>
     </row>
@@ -4876,16 +4852,21 @@
     </row>
     <row r="32" spans="1:2" ht="16.5" customHeight="1">
       <c r="A32" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="16.5" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="F2:G2"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -4897,11 +4878,6 @@
     <mergeCell ref="D9:E9"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:E2"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="F2:G2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/app/data/RAG 系统评估指标结果.xlsx
+++ b/src/app/data/RAG 系统评估指标结果.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/laixiangran/lai-workspace/ai-learn/src/app/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A23C540-CB69-714E-BD56-4B7FF84EB0D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEB90052-57A4-ED44-AAE5-5F1D0CDFC840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="1" xr2:uid="{752BAC88-3D22-6345-9E5D-6A586CA68B77}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="4" xr2:uid="{752BAC88-3D22-6345-9E5D-6A586CA68B77}"/>
   </bookViews>
   <sheets>
     <sheet name="06_检索优化 (1)" sheetId="5" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="104">
   <si>
     <t>版本</t>
   </si>
@@ -700,12 +700,27 @@
     <t>一句话总结：答案正确性越高，LLM 回答越准确。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>在不同优化阶段需要重点关注的指标：</t>
+  </si>
+  <si>
+    <t>问题优化：上下文召回率、答案正确性；</t>
+  </si>
+  <si>
+    <t>切分优化：上下文召回率、上下文相关性、答案正确性；</t>
+  </si>
+  <si>
+    <t>检索优化：上下文召回率、上下文相关性、答案正确性；</t>
+  </si>
+  <si>
+    <t>生成优化：答案忠实度、答案相关性、答案正确性。</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -848,6 +863,15 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -943,7 +967,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1071,6 +1095,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4670,10 +4697,10 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="28.83203125" customWidth="1"/>
+    <col min="1" max="1" width="53.1640625" customWidth="1"/>
     <col min="2" max="2" width="44.5" customWidth="1"/>
     <col min="3" max="3" width="37.1640625" customWidth="1"/>
     <col min="4" max="4" width="28.6640625" customWidth="1"/>
@@ -4860,13 +4887,33 @@
         <v>44</v>
       </c>
     </row>
+    <row r="36" spans="1:1" ht="16.5" customHeight="1">
+      <c r="A36" s="43" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" ht="16.5" customHeight="1">
+      <c r="A37" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" ht="16.5" customHeight="1">
+      <c r="A38" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" ht="16.5" customHeight="1">
+      <c r="A39" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" ht="16.5" customHeight="1">
+      <c r="A40" t="s">
+        <v>103</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="F2:G2"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -4878,6 +4925,11 @@
     <mergeCell ref="D9:E9"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:E2"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="F2:G2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
